--- a/new_versions_v4.2/ГОСТ_2177_метод_А_v3.13_контракт_с_генератором.xlsx
+++ b/new_versions_v4.2/ГОСТ_2177_метод_А_v3.13_контракт_с_генератором.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аудит_НД" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Техдолг" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Контракт_v313" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUM_u(T)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр_НД" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Аудит_НД'!$A$1:$G$13</definedName>
@@ -2278,6 +2280,1460 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>GUM-МОДЕЛЬ НЕОПРЕДЕЛЁННОСТИ T_corr(V) — fraction_lib.uncertainty (TD-2177-007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Модель:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T_corr = MROUND(T_obs + 0.0009*(101.3 - p_кПа)*(273 + t_bar) + ΔT_m; 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Источник чисел:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>python -m fraction_lib.excel_generator (этот лист генерируется, не редактировать вручную)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Условия прогона:</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>p = 700.0 мм рт.ст. = 93.326 кПа;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>t_bar = 20.0 °C (при отсутствии ввода принят 20 °C);</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>флаги политики: (нет)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>= 1. Компоненты бюджета (u_i, приведённые к °C) ==</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Распределение</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Полуширина</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Чувствительность c_i</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>u_i, °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>u1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Наблюдение T_obs (цена деления, прямоугольный)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2887</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>u2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Барометрическое давление p</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>кПа</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2637</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0761</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>u3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Температура барометра t_bar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007177</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>u4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Поправка выступающей нити barometer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.007177</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>u5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Цифровая номограмма ΔT_m (остаток оцифровки)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1732</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>u6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Дискретизация округления MROUND 0.5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>rectangular</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1443</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>u_c (комбинированная), °C:</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3741</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>k использованный:</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>| ν_eff:</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>| t95(ν_eff):</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>U = k·u_c, °C:</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7482</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>valid_for_reporting:</t>
+        </is>
+      </c>
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <f>= 2. Сквозной профиль U по точкам книги ==</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>% отгона</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T_corr_ref, °C</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>u_c, °C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>U, °C</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ν_eff</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>t95</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>valid_for_reporting</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Компоненты u_i (°C)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Замечания</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>133.9088</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>155.5636</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" t="n">
+        <v>161.355</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" t="n">
+        <v>166.1392</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="n">
+        <v>171.6788</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>174.1968</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B28" t="n">
+        <v>176.7148</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>35</v>
+      </c>
+      <c r="B29" t="n">
+        <v>179.2328</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40</v>
+      </c>
+      <c r="B30" t="n">
+        <v>183.0098</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>45</v>
+      </c>
+      <c r="B31" t="n">
+        <v>185.276</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>50</v>
+      </c>
+      <c r="B32" t="n">
+        <v>188.8012</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>55</v>
+      </c>
+      <c r="B33" t="n">
+        <v>191.3192</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>60</v>
+      </c>
+      <c r="B34" t="n">
+        <v>195.0962</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>65</v>
+      </c>
+      <c r="B35" t="n">
+        <v>198.3696</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>70</v>
+      </c>
+      <c r="B36" t="n">
+        <v>201.8948</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>75</v>
+      </c>
+      <c r="B37" t="n">
+        <v>204.4128</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>80</v>
+      </c>
+      <c r="B38" t="n">
+        <v>209.9524</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>85</v>
+      </c>
+      <c r="B39" t="n">
+        <v>214.4848</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>90</v>
+      </c>
+      <c r="B40" t="n">
+        <v>220.0244</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>95</v>
+      </c>
+      <c r="B41" t="n">
+        <v>227.5784</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>237.9022</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>u1=0.289, u2=0.076, u3=0.002, u4=0.001, u5=0.173, u6=0.144</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Как использовать: U из этого листа — расширенная неопределённость (k eff.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>скорректированной температуры отгона; применять вместе с флагами политики</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>из листа «Контракт_v313». При valid_for_reporting=FALSE точка вне канона НД.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>РЕЕСТР РЕДАКЦИЙ НД (docs/ND_REGISTRY.json) — TD-2177-008 / TD-D86-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Эта книга верифицирована редакцией:</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ГОСТ 2177-99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Статус сверки хешей (drift-guard):</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OK — константы кода соответствуют реестру</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Обозначение</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Редакция</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Действует с</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Заменяет</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sha256 нормативного ядра</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Верифицировано (доказательства)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Область</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ND-2026-001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ГОСТ 2177-99</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Изм. №1 (введён 01.07.2021, приказ 896-ст) + Поправка 2023</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5b143c2b4b5090e6c3dc5141fd350c40fc6270a7e1cc1655f1bce146894effe9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fraction_lib/tests/test_gost2177.py; fraction_lib/tests/test_uncertainty_td2177007.py; fraction_lib/tests/test_procedure_td2177006.py; docs/TECHDEBT_TD2177_002.md; docs/TECHDEBT_TD2177_004.md; docs/TECHDEBT_TD2177_005.md; docs/TECHDEBT_TD2177_007.md</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fraction_lib.gost2177, fraction_lib.uncertainty, fraction_lib.procedure; книги ГОСТ_2177_метод_А v3.12/v3.13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kPa-форма 0.0009*(101.3-p)*(273+t) эквивалентна нормативной 0.0000009*(101300-Pb)*(273+t) — осознанно не менялась (аудит G2177-N03).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ND-2026-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ASTM D86</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D86-23 (+ae1)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>9d600b919fec365ed73df472b37227bc42f2f66035592abc312d45920028a67d</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fraction_lib/tests/test_d86.py; fraction_lib/tests/test_excel_contract.py; docs (лист Аудит_НД книги v3.12)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fraction_lib.d86; книги ASTM_D86_ручной_метод v3.12/v3.13; автоматический метод v3.11 (частично)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Единая формула Lc для P&gt;760 внедрена в v3.12 и fraction_lib (TD-D86-001 часть book закрыта коммитом 1322c85). Сингулярность P≈820 мм рт. ст. — warning-слой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ND-LEGACY-001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ASTM D86</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D86-20a</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>исторические книги v3.11 и раннее</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Заменена на ND-2026-002 (D86-23). Расчёт по этой редакции запрещён resolve_for_calculation().</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Правила: запись неизменяема; новая редакция = новая запись + supersedes;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>расчёт по WITHDRAWN/SUPERSEDED запрещён (resolve_for_calculation);</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>изменение существенных констант без переоформления реестра блокирует CI (pytest).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
